--- a/Scripts/Логика работы.xlsx
+++ b/Scripts/Логика работы.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\Best_photo_ai\Scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68B6F6D2-7890-4124-9F48-5F8A8DB7F89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A144190-8260-40CD-A7EB-D4C5F82E670F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A2D7B961-CCCC-479A-8941-196B9820C830}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
